--- a/Listone.xlsx
+++ b/Listone.xlsx
@@ -1,22 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="153222"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stef9\Dropbox\Il mio PC (LAPTOP-VN45MR7H)\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="6" rupBuild="4505"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9264"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9270"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+  <calcPr calcId="124519"/>
+  <extLst xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -1697,8 +1692,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1794,7 +1789,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1829,7 +1824,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2006,30 +2001,30 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I525"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="6" style="1" customWidth="1"/>
-    <col min="2" max="2" width="3" style="1" customWidth="1"/>
-    <col min="3" max="3" width="21" style="1" customWidth="1"/>
-    <col min="4" max="4" width="12" style="1" customWidth="1"/>
-    <col min="5" max="5" width="6.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.88671875" style="2"/>
-    <col min="8" max="8" width="10.21875" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.88671875" style="2"/>
-    <col min="10" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="5" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="2.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.85546875" style="2"/>
+    <col min="8" max="8" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.85546875" style="2"/>
+    <col min="10" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2055,7 +2050,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8">
       <c r="A2" s="1">
         <v>5841</v>
       </c>
@@ -2069,10 +2064,10 @@
         <v>6</v>
       </c>
       <c r="E2" s="2">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="1">
         <v>5116</v>
       </c>
@@ -2089,7 +2084,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8">
       <c r="A4" s="1">
         <v>4431</v>
       </c>
@@ -2106,7 +2101,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8">
       <c r="A5" s="1">
         <v>6966</v>
       </c>
@@ -2123,7 +2118,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8">
       <c r="A6" s="1">
         <v>4964</v>
       </c>
@@ -2140,7 +2135,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8">
       <c r="A7" s="1">
         <v>4312</v>
       </c>
@@ -2157,7 +2152,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8">
       <c r="A8" s="1">
         <v>2521</v>
       </c>
@@ -2174,7 +2169,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8">
       <c r="A9" s="1">
         <v>572</v>
       </c>
@@ -2191,7 +2186,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8">
       <c r="A10" s="1">
         <v>133</v>
       </c>
@@ -2208,7 +2203,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8">
       <c r="A11" s="1">
         <v>4360</v>
       </c>
@@ -2225,7 +2220,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8">
       <c r="A12" s="1">
         <v>6482</v>
       </c>
@@ -2242,7 +2237,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8">
       <c r="A13" s="1">
         <v>2134</v>
       </c>
@@ -2259,7 +2254,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8">
       <c r="A14" s="1">
         <v>6462</v>
       </c>
@@ -2276,7 +2271,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8">
       <c r="A15" s="1">
         <v>6534</v>
       </c>
@@ -2293,7 +2288,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8">
       <c r="A16" s="1">
         <v>7332</v>
       </c>
@@ -2310,7 +2305,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5">
       <c r="A17" s="1">
         <v>7411</v>
       </c>
@@ -2327,7 +2322,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5">
       <c r="A18" s="1">
         <v>4236</v>
       </c>
@@ -2344,7 +2339,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5">
       <c r="A19" s="1">
         <v>6248</v>
       </c>
@@ -2361,7 +2356,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5">
       <c r="A20" s="1">
         <v>6415</v>
       </c>
@@ -2378,7 +2373,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5">
       <c r="A21" s="1">
         <v>4485</v>
       </c>
@@ -2395,7 +2390,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5">
       <c r="A22" s="1">
         <v>2170</v>
       </c>
@@ -2412,7 +2407,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5">
       <c r="A23" s="1">
         <v>7463</v>
       </c>
@@ -2429,7 +2424,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5">
       <c r="A24" s="1">
         <v>2814</v>
       </c>
@@ -2446,7 +2441,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5">
       <c r="A25" s="1">
         <v>4</v>
       </c>
@@ -2463,7 +2458,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5">
       <c r="A26" s="1">
         <v>7533</v>
       </c>
@@ -2480,7 +2475,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5">
       <c r="A27" s="1">
         <v>7172</v>
       </c>
@@ -2497,7 +2492,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5">
       <c r="A28" s="1">
         <v>6650</v>
       </c>
@@ -2514,7 +2509,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5">
       <c r="A29" s="1">
         <v>7301</v>
       </c>
@@ -2531,7 +2526,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5">
       <c r="A30" s="1">
         <v>2809</v>
       </c>
@@ -2548,7 +2543,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5">
       <c r="A31" s="1">
         <v>6403</v>
       </c>
@@ -2565,7 +2560,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5">
       <c r="A32" s="1">
         <v>158</v>
       </c>
@@ -2582,7 +2577,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5">
       <c r="A33" s="1">
         <v>7466</v>
       </c>
@@ -2599,7 +2594,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5">
       <c r="A34" s="1">
         <v>219</v>
       </c>
@@ -2616,7 +2611,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5">
       <c r="A35" s="1">
         <v>6569</v>
       </c>
@@ -2633,7 +2628,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5">
       <c r="A36" s="1">
         <v>1926</v>
       </c>
@@ -2650,7 +2645,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5">
       <c r="A37" s="1">
         <v>1930</v>
       </c>
@@ -2667,7 +2662,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5">
       <c r="A38" s="1">
         <v>7337</v>
       </c>
@@ -2684,7 +2679,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5">
       <c r="A39" s="1">
         <v>7534</v>
       </c>
@@ -2701,7 +2696,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5">
       <c r="A40" s="1">
         <v>2815</v>
       </c>
@@ -2718,7 +2713,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5">
       <c r="A41" s="1">
         <v>6813</v>
       </c>
@@ -2735,7 +2730,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5">
       <c r="A42" s="1">
         <v>7475</v>
       </c>
@@ -2752,7 +2747,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5">
       <c r="A43" s="1">
         <v>2845</v>
       </c>
@@ -2769,7 +2764,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5">
       <c r="A44" s="1">
         <v>6662</v>
       </c>
@@ -2786,7 +2781,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5">
       <c r="A45" s="1">
         <v>7048</v>
       </c>
@@ -2803,7 +2798,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5">
       <c r="A46" s="1">
         <v>610</v>
       </c>
@@ -2820,7 +2815,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5">
       <c r="A47" s="1">
         <v>4518</v>
       </c>
@@ -2837,7 +2832,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5">
       <c r="A48" s="1">
         <v>4867</v>
       </c>
@@ -2854,7 +2849,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5">
       <c r="A49" s="1">
         <v>7457</v>
       </c>
@@ -2871,7 +2866,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5">
       <c r="A50" s="1">
         <v>5320</v>
       </c>
@@ -2888,7 +2883,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5">
       <c r="A51" s="1">
         <v>7363</v>
       </c>
@@ -2905,7 +2900,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5">
       <c r="A52" s="1">
         <v>543</v>
       </c>
@@ -2922,7 +2917,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5">
       <c r="A53" s="1">
         <v>5707</v>
       </c>
@@ -2939,7 +2934,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5">
       <c r="A54" s="1">
         <v>6671</v>
       </c>
@@ -2956,7 +2951,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:5">
       <c r="A55" s="1">
         <v>7531</v>
       </c>
@@ -2973,7 +2968,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:5">
       <c r="A56" s="1">
         <v>7545</v>
       </c>
@@ -2990,7 +2985,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:5">
       <c r="A57" s="1">
         <v>2127</v>
       </c>
@@ -3007,7 +3002,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5">
       <c r="A58" s="1">
         <v>7557</v>
       </c>
@@ -3024,7 +3019,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:5">
       <c r="A59" s="1">
         <v>7560</v>
       </c>
@@ -3041,7 +3036,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:5">
       <c r="A60" s="1">
         <v>3</v>
       </c>
@@ -3058,7 +3053,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:5">
       <c r="A61" s="1">
         <v>4957</v>
       </c>
@@ -3075,7 +3070,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:5">
       <c r="A62" s="1">
         <v>4468</v>
       </c>
@@ -3092,7 +3087,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:5">
       <c r="A63" s="1">
         <v>7603</v>
       </c>
@@ -3109,7 +3104,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:5">
       <c r="A64" s="1">
         <v>7611</v>
       </c>
@@ -3126,7 +3121,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:5">
       <c r="A65" s="1">
         <v>254</v>
       </c>
@@ -3143,7 +3138,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:5">
       <c r="A66" s="1">
         <v>4998</v>
       </c>
@@ -3160,7 +3155,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:5">
       <c r="A67" s="1">
         <v>7181</v>
       </c>
@@ -3177,7 +3172,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:5">
       <c r="A68" s="1">
         <v>4159</v>
       </c>
@@ -3194,7 +3189,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:5">
       <c r="A69" s="1">
         <v>2788</v>
       </c>
@@ -3211,7 +3206,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:5">
       <c r="A70" s="1">
         <v>2296</v>
       </c>
@@ -3228,7 +3223,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:5">
       <c r="A71" s="1">
         <v>2120</v>
       </c>
@@ -3245,7 +3240,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:5">
       <c r="A72" s="1">
         <v>5022</v>
       </c>
@@ -3262,7 +3257,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:5">
       <c r="A73" s="1">
         <v>4409</v>
       </c>
@@ -3279,7 +3274,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:5">
       <c r="A74" s="1">
         <v>4976</v>
       </c>
@@ -3296,7 +3291,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:5">
       <c r="A75" s="1">
         <v>4317</v>
       </c>
@@ -3313,7 +3308,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:5">
       <c r="A76" s="1">
         <v>6956</v>
       </c>
@@ -3330,7 +3325,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:5">
       <c r="A77" s="1">
         <v>6217</v>
       </c>
@@ -3347,7 +3342,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:5">
       <c r="A78" s="1">
         <v>2514</v>
       </c>
@@ -3364,7 +3359,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:5">
       <c r="A79" s="1">
         <v>5833</v>
       </c>
@@ -3381,7 +3376,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:5">
       <c r="A80" s="1">
         <v>2816</v>
       </c>
@@ -3398,7 +3393,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:5">
       <c r="A81" s="1">
         <v>5982</v>
       </c>
@@ -3415,7 +3410,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:5">
       <c r="A82" s="1">
         <v>5750</v>
       </c>
@@ -3432,7 +3427,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:5">
       <c r="A83" s="1">
         <v>5526</v>
       </c>
@@ -3449,7 +3444,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:5">
       <c r="A84" s="1">
         <v>6869</v>
       </c>
@@ -3466,7 +3461,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:5">
       <c r="A85" s="1">
         <v>5885</v>
       </c>
@@ -3483,7 +3478,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:5">
       <c r="A86" s="1">
         <v>4807</v>
       </c>
@@ -3500,7 +3495,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:5">
       <c r="A87" s="1">
         <v>5514</v>
       </c>
@@ -3517,7 +3512,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:5">
       <c r="A88" s="1">
         <v>5520</v>
       </c>
@@ -3534,7 +3529,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:5">
       <c r="A89" s="1">
         <v>6989</v>
       </c>
@@ -3551,7 +3546,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:5">
       <c r="A90" s="1">
         <v>5641</v>
       </c>
@@ -3568,7 +3563,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:5">
       <c r="A91" s="1">
         <v>6046</v>
       </c>
@@ -3585,7 +3580,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:5">
       <c r="A92" s="1">
         <v>554</v>
       </c>
@@ -3602,7 +3597,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:5">
       <c r="A93" s="1">
         <v>6042</v>
       </c>
@@ -3619,7 +3614,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:5">
       <c r="A94" s="1">
         <v>4734</v>
       </c>
@@ -3636,7 +3631,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:5">
       <c r="A95" s="1">
         <v>4210</v>
       </c>
@@ -3653,7 +3648,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:5">
       <c r="A96" s="1">
         <v>6531</v>
       </c>
@@ -3670,7 +3665,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:5">
       <c r="A97" s="1">
         <v>6814</v>
       </c>
@@ -3687,7 +3682,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:5">
       <c r="A98" s="1">
         <v>4657</v>
       </c>
@@ -3704,7 +3699,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:5">
       <c r="A99" s="1">
         <v>6320</v>
       </c>
@@ -3721,7 +3716,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:5">
       <c r="A100" s="1">
         <v>6496</v>
       </c>
@@ -3738,7 +3733,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:5">
       <c r="A101" s="1">
         <v>1852</v>
       </c>
@@ -3755,7 +3750,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:5">
       <c r="A102" s="1">
         <v>6664</v>
       </c>
@@ -3772,7 +3767,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:5">
       <c r="A103" s="1">
         <v>5862</v>
       </c>
@@ -3789,7 +3784,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:5">
       <c r="A104" s="1">
         <v>7529</v>
       </c>
@@ -3806,7 +3801,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:5">
       <c r="A105" s="1">
         <v>4994</v>
       </c>
@@ -3823,7 +3818,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:5">
       <c r="A106" s="1">
         <v>5555</v>
       </c>
@@ -3840,7 +3835,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:5">
       <c r="A107" s="1">
         <v>6727</v>
       </c>
@@ -3857,7 +3852,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:5">
       <c r="A108" s="1">
         <v>5675</v>
       </c>
@@ -3874,7 +3869,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:5">
       <c r="A109" s="1">
         <v>5701</v>
       </c>
@@ -3891,7 +3886,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:5">
       <c r="A110" s="1">
         <v>7414</v>
       </c>
@@ -3908,7 +3903,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:5">
       <c r="A111" s="1">
         <v>5365</v>
       </c>
@@ -3925,7 +3920,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:5">
       <c r="A112" s="1">
         <v>5877</v>
       </c>
@@ -3942,7 +3937,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:5">
       <c r="A113" s="1">
         <v>460</v>
       </c>
@@ -3959,7 +3954,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:5">
       <c r="A114" s="1">
         <v>4401</v>
       </c>
@@ -3976,7 +3971,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:5">
       <c r="A115" s="1">
         <v>4751</v>
       </c>
@@ -3993,7 +3988,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:5">
       <c r="A116" s="1">
         <v>2724</v>
       </c>
@@ -4010,7 +4005,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:5">
       <c r="A117" s="1">
         <v>6672</v>
       </c>
@@ -4027,7 +4022,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:5">
       <c r="A118" s="1">
         <v>6642</v>
       </c>
@@ -4044,7 +4039,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:5">
       <c r="A119" s="1">
         <v>5010</v>
       </c>
@@ -4061,7 +4056,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:5">
       <c r="A120" s="1">
         <v>6485</v>
       </c>
@@ -4078,7 +4073,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:5">
       <c r="A121" s="1">
         <v>4664</v>
       </c>
@@ -4095,7 +4090,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:5">
       <c r="A122" s="1">
         <v>7580</v>
       </c>
@@ -4112,7 +4107,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:5">
       <c r="A123" s="1">
         <v>6916</v>
       </c>
@@ -4129,7 +4124,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:5">
       <c r="A124" s="1">
         <v>4887</v>
       </c>
@@ -4146,7 +4141,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:5">
       <c r="A125" s="1">
         <v>7219</v>
       </c>
@@ -4163,7 +4158,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:5">
       <c r="A126" s="1">
         <v>7212</v>
       </c>
@@ -4180,7 +4175,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:5">
       <c r="A127" s="1">
         <v>4433</v>
       </c>
@@ -4197,7 +4192,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:5">
       <c r="A128" s="1">
         <v>6867</v>
       </c>
@@ -4214,7 +4209,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:5">
       <c r="A129" s="1">
         <v>7294</v>
       </c>
@@ -4231,7 +4226,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:5">
       <c r="A130" s="1">
         <v>7410</v>
       </c>
@@ -4248,7 +4243,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:5">
       <c r="A131" s="1">
         <v>4952</v>
       </c>
@@ -4265,7 +4260,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:5">
       <c r="A132" s="1">
         <v>6660</v>
       </c>
@@ -4282,7 +4277,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:5">
       <c r="A133" s="1">
         <v>4177</v>
       </c>
@@ -4299,7 +4294,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:5">
       <c r="A134" s="1">
         <v>5620</v>
       </c>
@@ -4316,7 +4311,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:5">
       <c r="A135" s="1">
         <v>2188</v>
       </c>
@@ -4333,7 +4328,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:5">
       <c r="A136" s="1">
         <v>6632</v>
       </c>
@@ -4350,7 +4345,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:5">
       <c r="A137" s="1">
         <v>6990</v>
       </c>
@@ -4367,7 +4362,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:5">
       <c r="A138" s="1">
         <v>4502</v>
       </c>
@@ -4384,7 +4379,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:5">
       <c r="A139" s="1">
         <v>7485</v>
       </c>
@@ -4401,7 +4396,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:5">
       <c r="A140" s="1">
         <v>6202</v>
       </c>
@@ -4418,7 +4413,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:5">
       <c r="A141" s="1">
         <v>6495</v>
       </c>
@@ -4435,7 +4430,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:5">
       <c r="A142" s="1">
         <v>7253</v>
       </c>
@@ -4452,7 +4447,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:5">
       <c r="A143" s="1">
         <v>7329</v>
       </c>
@@ -4469,7 +4464,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:5">
       <c r="A144" s="1">
         <v>4705</v>
       </c>
@@ -4486,7 +4481,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:5">
       <c r="A145" s="1">
         <v>2640</v>
       </c>
@@ -4503,7 +4498,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:5">
       <c r="A146" s="1">
         <v>7068</v>
       </c>
@@ -4520,7 +4515,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:5">
       <c r="A147" s="1">
         <v>5678</v>
       </c>
@@ -4537,7 +4532,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:5">
       <c r="A148" s="1">
         <v>7532</v>
       </c>
@@ -4554,7 +4549,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:5">
       <c r="A149" s="1">
         <v>7274</v>
       </c>
@@ -4571,7 +4566,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:5">
       <c r="A150" s="1">
         <v>6893</v>
       </c>
@@ -4588,7 +4583,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:5">
       <c r="A151" s="1">
         <v>5449</v>
       </c>
@@ -4605,7 +4600,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:5">
       <c r="A152" s="1">
         <v>7469</v>
       </c>
@@ -4622,7 +4617,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:5">
       <c r="A153" s="1">
         <v>6238</v>
       </c>
@@ -4639,7 +4634,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:5">
       <c r="A154" s="1">
         <v>2593</v>
       </c>
@@ -4656,7 +4651,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:5">
       <c r="A155" s="1">
         <v>6766</v>
       </c>
@@ -4673,7 +4668,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:5">
       <c r="A156" s="1">
         <v>4817</v>
       </c>
@@ -4690,7 +4685,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:5">
       <c r="A157" s="1">
         <v>7240</v>
       </c>
@@ -4707,7 +4702,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:5">
       <c r="A158" s="1">
         <v>5840</v>
       </c>
@@ -4724,7 +4719,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:5">
       <c r="A159" s="1">
         <v>6986</v>
       </c>
@@ -4741,7 +4736,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:5">
       <c r="A160" s="1">
         <v>6890</v>
       </c>
@@ -4758,7 +4753,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:5">
       <c r="A161" s="1">
         <v>4845</v>
       </c>
@@ -4775,7 +4770,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:5">
       <c r="A162" s="1">
         <v>5695</v>
       </c>
@@ -4792,7 +4787,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:5">
       <c r="A163" s="1">
         <v>7069</v>
       </c>
@@ -4809,7 +4804,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:5">
       <c r="A164" s="1">
         <v>7564</v>
       </c>
@@ -4826,7 +4821,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:5">
       <c r="A165" s="1">
         <v>7268</v>
       </c>
@@ -4843,7 +4838,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:5">
       <c r="A166" s="1">
         <v>7014</v>
       </c>
@@ -4860,7 +4855,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:5">
       <c r="A167" s="1">
         <v>5603</v>
       </c>
@@ -4877,7 +4872,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:5">
       <c r="A168" s="1">
         <v>7467</v>
       </c>
@@ -4894,7 +4889,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:5">
       <c r="A169" s="1">
         <v>7537</v>
       </c>
@@ -4911,7 +4906,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:5">
       <c r="A170" s="1">
         <v>5831</v>
       </c>
@@ -4928,7 +4923,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:5">
       <c r="A171" s="1">
         <v>5739</v>
       </c>
@@ -4945,7 +4940,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:5">
       <c r="A172" s="1">
         <v>5273</v>
       </c>
@@ -4962,7 +4957,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:5">
       <c r="A173" s="1">
         <v>2115</v>
       </c>
@@ -4979,7 +4974,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:5">
       <c r="A174" s="1">
         <v>6659</v>
       </c>
@@ -4996,7 +4991,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:5">
       <c r="A175" s="1">
         <v>5838</v>
       </c>
@@ -5013,7 +5008,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:5">
       <c r="A176" s="1">
         <v>7235</v>
       </c>
@@ -5030,7 +5025,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:5">
       <c r="A177" s="1">
         <v>5307</v>
       </c>
@@ -5047,7 +5042,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:5">
       <c r="A178" s="1">
         <v>6631</v>
       </c>
@@ -5064,7 +5059,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:5">
       <c r="A179" s="1">
         <v>4374</v>
       </c>
@@ -5081,7 +5076,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:5">
       <c r="A180" s="1">
         <v>5851</v>
       </c>
@@ -5098,7 +5093,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:5">
       <c r="A181" s="1">
         <v>7526</v>
       </c>
@@ -5115,7 +5110,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:5">
       <c r="A182" s="1">
         <v>4263</v>
       </c>
@@ -5132,7 +5127,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:5">
       <c r="A183" s="1">
         <v>5820</v>
       </c>
@@ -5149,7 +5144,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:5">
       <c r="A184" s="1">
         <v>5527</v>
       </c>
@@ -5166,7 +5161,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:5">
       <c r="A185" s="1">
         <v>7312</v>
       </c>
@@ -5183,7 +5178,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:5">
       <c r="A186" s="1">
         <v>7538</v>
       </c>
@@ -5200,7 +5195,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:5">
       <c r="A187" s="1">
         <v>4375</v>
       </c>
@@ -5217,7 +5212,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:5">
       <c r="A188" s="1">
         <v>7563</v>
       </c>
@@ -5234,7 +5229,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:5">
       <c r="A189" s="1">
         <v>5578</v>
       </c>
@@ -5251,7 +5246,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:5">
       <c r="A190" s="1">
         <v>5498</v>
       </c>
@@ -5268,7 +5263,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:5">
       <c r="A191" s="1">
         <v>7326</v>
       </c>
@@ -5285,7 +5280,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:5">
       <c r="A192" s="1">
         <v>7125</v>
       </c>
@@ -5302,7 +5297,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:5">
       <c r="A193" s="1">
         <v>4378</v>
       </c>
@@ -5319,7 +5314,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:5">
       <c r="A194" s="1">
         <v>7175</v>
       </c>
@@ -5336,7 +5331,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:5">
       <c r="A195" s="1">
         <v>7540</v>
       </c>
@@ -5353,7 +5348,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:5">
       <c r="A196" s="1">
         <v>5757</v>
       </c>
@@ -5370,7 +5365,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:5">
       <c r="A197" s="1">
         <v>7012</v>
       </c>
@@ -5387,7 +5382,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:5">
       <c r="A198" s="1">
         <v>7131</v>
       </c>
@@ -5404,7 +5399,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:5">
       <c r="A199" s="1">
         <v>7238</v>
       </c>
@@ -5421,7 +5416,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:5">
       <c r="A200" s="1">
         <v>4925</v>
       </c>
@@ -5438,7 +5433,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:5">
       <c r="A201" s="1">
         <v>7255</v>
       </c>
@@ -5455,7 +5450,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:5">
       <c r="A202" s="1">
         <v>6985</v>
       </c>
@@ -5472,7 +5467,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:5">
       <c r="A203" s="1">
         <v>6925</v>
       </c>
@@ -5489,7 +5484,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:5">
       <c r="A204" s="1">
         <v>5994</v>
       </c>
@@ -5506,7 +5501,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:5">
       <c r="A205" s="1">
         <v>6892</v>
       </c>
@@ -5523,7 +5518,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:5">
       <c r="A206" s="1">
         <v>6673</v>
       </c>
@@ -5540,7 +5535,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:5">
       <c r="A207" s="1">
         <v>6821</v>
       </c>
@@ -5557,7 +5552,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:5">
       <c r="A208" s="1">
         <v>7154</v>
       </c>
@@ -5574,7 +5569,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:5">
       <c r="A209" s="1">
         <v>7605</v>
       </c>
@@ -5591,7 +5586,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:5">
       <c r="A210" s="1">
         <v>6601</v>
       </c>
@@ -5608,7 +5603,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:5">
       <c r="A211" s="1">
         <v>7483</v>
       </c>
@@ -5625,7 +5620,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:5">
       <c r="A212" s="1">
         <v>6896</v>
       </c>
@@ -5642,7 +5637,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:5">
       <c r="A213" s="1">
         <v>6977</v>
       </c>
@@ -5659,7 +5654,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:5">
       <c r="A214" s="1">
         <v>7413</v>
       </c>
@@ -5676,7 +5671,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:5">
       <c r="A215" s="1">
         <v>791</v>
       </c>
@@ -5693,7 +5688,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:5">
       <c r="A216" s="1">
         <v>2263</v>
       </c>
@@ -5710,7 +5705,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:5">
       <c r="A217" s="1">
         <v>2728</v>
       </c>
@@ -5727,7 +5722,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:5">
       <c r="A218" s="1">
         <v>6883</v>
       </c>
@@ -5744,7 +5739,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:5">
       <c r="A219" s="1">
         <v>7182</v>
       </c>
@@ -5761,7 +5756,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:5">
       <c r="A220" s="1">
         <v>7525</v>
       </c>
@@ -5778,7 +5773,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:5">
       <c r="A221" s="1">
         <v>7476</v>
       </c>
@@ -5795,7 +5790,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:5">
       <c r="A222" s="1">
         <v>6638</v>
       </c>
@@ -5812,7 +5807,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:5">
       <c r="A223" s="1">
         <v>7202</v>
       </c>
@@ -5829,7 +5824,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:5">
       <c r="A224" s="1">
         <v>252</v>
       </c>
@@ -5846,7 +5841,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:5">
       <c r="A225" s="1">
         <v>6021</v>
       </c>
@@ -5863,7 +5858,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:5">
       <c r="A226" s="1">
         <v>7478</v>
       </c>
@@ -5880,7 +5875,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:5">
       <c r="A227" s="1">
         <v>6681</v>
       </c>
@@ -5897,7 +5892,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:5">
       <c r="A228" s="1">
         <v>7548</v>
       </c>
@@ -5914,7 +5909,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:5">
       <c r="A229" s="1">
         <v>7573</v>
       </c>
@@ -5931,7 +5926,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:5">
       <c r="A230" s="1">
         <v>5812</v>
       </c>
@@ -5948,7 +5943,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:5">
       <c r="A231" s="1">
         <v>487</v>
       </c>
@@ -5965,7 +5960,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:5">
       <c r="A232" s="1">
         <v>418</v>
       </c>
@@ -5982,7 +5977,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:5">
       <c r="A233" s="1">
         <v>5424</v>
       </c>
@@ -5999,7 +5994,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:5">
       <c r="A234" s="1">
         <v>294</v>
       </c>
@@ -6016,7 +6011,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:5">
       <c r="A235" s="1">
         <v>6039</v>
       </c>
@@ -6033,7 +6028,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:5">
       <c r="A236" s="1">
         <v>327</v>
       </c>
@@ -6050,7 +6045,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:5">
       <c r="A237" s="1">
         <v>5399</v>
       </c>
@@ -6067,7 +6062,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:5">
       <c r="A238" s="1">
         <v>6809</v>
       </c>
@@ -6084,7 +6079,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="239" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:5">
       <c r="A239" s="1">
         <v>5481</v>
       </c>
@@ -6101,7 +6096,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:5">
       <c r="A240" s="1">
         <v>6149</v>
       </c>
@@ -6118,7 +6113,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="241" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:5">
       <c r="A241" s="1">
         <v>7260</v>
       </c>
@@ -6135,7 +6130,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="242" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:5">
       <c r="A242" s="1">
         <v>6189</v>
       </c>
@@ -6152,7 +6147,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="243" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:5">
       <c r="A243" s="1">
         <v>7156</v>
       </c>
@@ -6169,7 +6164,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="244" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:5">
       <c r="A244" s="1">
         <v>7356</v>
       </c>
@@ -6186,7 +6181,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="245" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:5">
       <c r="A245" s="1">
         <v>7454</v>
       </c>
@@ -6203,7 +6198,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="246" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:5">
       <c r="A246" s="1">
         <v>7553</v>
       </c>
@@ -6220,7 +6215,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="247" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:5">
       <c r="A247" s="1">
         <v>7396</v>
       </c>
@@ -6237,7 +6232,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="248" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:5">
       <c r="A248" s="1">
         <v>7599</v>
       </c>
@@ -6254,7 +6249,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="249" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:5">
       <c r="A249" s="1">
         <v>7604</v>
       </c>
@@ -6271,7 +6266,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="250" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:5">
       <c r="A250" s="1">
         <v>7615</v>
       </c>
@@ -6288,7 +6283,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="251" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:5">
       <c r="A251" s="1">
         <v>6826</v>
       </c>
@@ -6305,7 +6300,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="252" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:5">
       <c r="A252" s="1">
         <v>6875</v>
       </c>
@@ -6322,7 +6317,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="253" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:5">
       <c r="A253" s="1">
         <v>2194</v>
       </c>
@@ -6339,7 +6334,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="254" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:5">
       <c r="A254" s="1">
         <v>4777</v>
       </c>
@@ -6356,7 +6351,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="255" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:5">
       <c r="A255" s="1">
         <v>2167</v>
       </c>
@@ -6373,7 +6368,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="256" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:5">
       <c r="A256" s="1">
         <v>2423</v>
       </c>
@@ -6390,7 +6385,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="257" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:5">
       <c r="A257" s="1">
         <v>2379</v>
       </c>
@@ -6407,7 +6402,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="258" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:5">
       <c r="A258" s="1">
         <v>7126</v>
       </c>
@@ -6424,7 +6419,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="259" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:5">
       <c r="A259" s="1">
         <v>7556</v>
       </c>
@@ -6441,7 +6436,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="260" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:5">
       <c r="A260" s="1">
         <v>5559</v>
       </c>
@@ -6458,7 +6453,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="261" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:5">
       <c r="A261" s="1">
         <v>2766</v>
       </c>
@@ -6475,7 +6470,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="262" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:5">
       <c r="A262" s="1">
         <v>1870</v>
       </c>
@@ -6492,7 +6487,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="263" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:5">
       <c r="A263" s="1">
         <v>4973</v>
       </c>
@@ -6509,7 +6504,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="264" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:5">
       <c r="A264" s="1">
         <v>6908</v>
       </c>
@@ -6526,7 +6521,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="265" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:5">
       <c r="A265" s="1">
         <v>632</v>
       </c>
@@ -6543,7 +6538,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="266" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:5">
       <c r="A266" s="1">
         <v>2517</v>
       </c>
@@ -6560,7 +6555,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="267" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:5">
       <c r="A267" s="1">
         <v>5800</v>
       </c>
@@ -6577,7 +6572,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="268" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:5">
       <c r="A268" s="1">
         <v>7314</v>
       </c>
@@ -6594,7 +6589,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="269" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:5">
       <c r="A269" s="1">
         <v>5687</v>
       </c>
@@ -6611,7 +6606,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="270" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:5">
       <c r="A270" s="1">
         <v>5792</v>
       </c>
@@ -6628,7 +6623,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="271" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:5">
       <c r="A271" s="1">
         <v>5119</v>
       </c>
@@ -6645,7 +6640,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="272" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:5">
       <c r="A272" s="1">
         <v>7129</v>
       </c>
@@ -6662,7 +6657,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="273" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:5">
       <c r="A273" s="1">
         <v>7436</v>
       </c>
@@ -6679,7 +6674,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="274" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:5">
       <c r="A274" s="1">
         <v>6884</v>
       </c>
@@ -6696,7 +6691,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="275" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:5">
       <c r="A275" s="1">
         <v>2606</v>
       </c>
@@ -6713,7 +6708,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="276" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:5">
       <c r="A276" s="1">
         <v>7078</v>
       </c>
@@ -6730,7 +6725,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="277" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:5">
       <c r="A277" s="1">
         <v>6372</v>
       </c>
@@ -6747,7 +6742,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="278" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:5">
       <c r="A278" s="1">
         <v>5172</v>
       </c>
@@ -6764,7 +6759,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="279" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:5">
       <c r="A279" s="1">
         <v>1850</v>
       </c>
@@ -6781,7 +6776,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="280" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:5">
       <c r="A280" s="1">
         <v>6844</v>
       </c>
@@ -6798,7 +6793,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="281" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:5">
       <c r="A281" s="1">
         <v>5823</v>
       </c>
@@ -6815,7 +6810,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="282" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:5">
       <c r="A282" s="1">
         <v>152</v>
       </c>
@@ -6832,7 +6827,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="283" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:5">
       <c r="A283" s="1">
         <v>4220</v>
       </c>
@@ -6849,7 +6844,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="284" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:5">
       <c r="A284" s="1">
         <v>6684</v>
       </c>
@@ -6866,7 +6861,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="285" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:5">
       <c r="A285" s="1">
         <v>4179</v>
       </c>
@@ -6883,7 +6878,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="286" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:5">
       <c r="A286" s="1">
         <v>6151</v>
       </c>
@@ -6900,7 +6895,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="287" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:5">
       <c r="A287" s="1">
         <v>5562</v>
       </c>
@@ -6917,7 +6912,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="288" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:5">
       <c r="A288" s="1">
         <v>4892</v>
       </c>
@@ -6934,7 +6929,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="289" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:5">
       <c r="A289" s="1">
         <v>536</v>
       </c>
@@ -6951,7 +6946,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="290" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:5">
       <c r="A290" s="1">
         <v>7223</v>
       </c>
@@ -6968,7 +6963,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="291" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:5">
       <c r="A291" s="1">
         <v>5589</v>
       </c>
@@ -6985,7 +6980,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="292" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:5">
       <c r="A292" s="1">
         <v>5844</v>
       </c>
@@ -7002,7 +6997,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="293" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:5">
       <c r="A293" s="1">
         <v>5888</v>
       </c>
@@ -7019,7 +7014,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="294" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:5">
       <c r="A294" s="1">
         <v>530</v>
       </c>
@@ -7036,7 +7031,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="295" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:5">
       <c r="A295" s="1">
         <v>2077</v>
       </c>
@@ -7053,7 +7048,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="296" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:5">
       <c r="A296" s="1">
         <v>184</v>
       </c>
@@ -7070,7 +7065,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="297" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:5">
       <c r="A297" s="1">
         <v>1933</v>
       </c>
@@ -7087,7 +7082,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="298" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:5">
       <c r="A298" s="1">
         <v>6274</v>
       </c>
@@ -7104,7 +7099,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="299" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:5">
       <c r="A299" s="1">
         <v>2848</v>
       </c>
@@ -7121,7 +7116,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="300" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:5">
       <c r="A300" s="1">
         <v>5500</v>
       </c>
@@ -7138,7 +7133,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="301" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:5">
       <c r="A301" s="1">
         <v>6398</v>
       </c>
@@ -7155,7 +7150,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="302" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:5">
       <c r="A302" s="1">
         <v>6717</v>
       </c>
@@ -7172,7 +7167,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="303" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:5">
       <c r="A303" s="1">
         <v>4364</v>
       </c>
@@ -7189,7 +7184,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="304" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:5">
       <c r="A304" s="1">
         <v>2765</v>
       </c>
@@ -7206,7 +7201,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="305" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:5">
       <c r="A305" s="1">
         <v>4436</v>
       </c>
@@ -7223,7 +7218,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="306" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:5">
       <c r="A306" s="1">
         <v>4465</v>
       </c>
@@ -7240,7 +7235,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="307" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:5">
       <c r="A307" s="1">
         <v>6294</v>
       </c>
@@ -7257,7 +7252,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="308" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:5">
       <c r="A308" s="1">
         <v>7070</v>
       </c>
@@ -7274,7 +7269,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="309" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:5">
       <c r="A309" s="1">
         <v>827</v>
       </c>
@@ -7291,7 +7286,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="310" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:5">
       <c r="A310" s="1">
         <v>5878</v>
       </c>
@@ -7308,7 +7303,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="311" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:5">
       <c r="A311" s="1">
         <v>4287</v>
       </c>
@@ -7325,7 +7320,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="312" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:5">
       <c r="A312" s="1">
         <v>779</v>
       </c>
@@ -7342,7 +7337,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="313" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:5">
       <c r="A313" s="1">
         <v>5735</v>
       </c>
@@ -7359,7 +7354,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="314" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:5">
       <c r="A314" s="1">
         <v>7551</v>
       </c>
@@ -7376,7 +7371,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="315" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:5">
       <c r="A315" s="1">
         <v>5858</v>
       </c>
@@ -7393,7 +7388,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="316" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:5">
       <c r="A316" s="1">
         <v>4870</v>
       </c>
@@ -7410,7 +7405,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="317" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:5">
       <c r="A317" s="1">
         <v>7311</v>
       </c>
@@ -7427,7 +7422,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="318" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:5">
       <c r="A318" s="1">
         <v>6010</v>
       </c>
@@ -7444,7 +7439,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="319" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:5">
       <c r="A319" s="1">
         <v>7472</v>
       </c>
@@ -7461,7 +7456,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="320" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:5">
       <c r="A320" s="1">
         <v>5791</v>
       </c>
@@ -7478,7 +7473,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="321" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:5">
       <c r="A321" s="1">
         <v>4459</v>
       </c>
@@ -7495,7 +7490,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="322" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:5">
       <c r="A322" s="1">
         <v>5504</v>
       </c>
@@ -7512,7 +7507,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="323" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:5">
       <c r="A323" s="1">
         <v>4856</v>
       </c>
@@ -7529,7 +7524,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="324" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:5">
       <c r="A324" s="1">
         <v>2741</v>
       </c>
@@ -7546,7 +7541,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="325" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:5">
       <c r="A325" s="1">
         <v>6666</v>
       </c>
@@ -7563,7 +7558,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="326" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:5">
       <c r="A326" s="1">
         <v>6190</v>
       </c>
@@ -7580,7 +7575,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="327" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:5">
       <c r="A327" s="1">
         <v>6218</v>
       </c>
@@ -7597,7 +7592,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="328" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:5">
       <c r="A328" s="1">
         <v>6680</v>
       </c>
@@ -7614,7 +7609,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="329" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:5">
       <c r="A329" s="1">
         <v>6783</v>
       </c>
@@ -7631,7 +7626,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="330" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:5">
       <c r="A330" s="1">
         <v>5946</v>
       </c>
@@ -7648,7 +7643,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="331" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:5">
       <c r="A331" s="1">
         <v>4479</v>
       </c>
@@ -7665,7 +7660,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="332" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:5">
       <c r="A332" s="1">
         <v>5422</v>
       </c>
@@ -7682,7 +7677,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="333" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:5">
       <c r="A333" s="1">
         <v>5298</v>
       </c>
@@ -7699,7 +7694,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="334" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:5">
       <c r="A334" s="1">
         <v>4260</v>
       </c>
@@ -7716,7 +7711,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="335" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:5">
       <c r="A335" s="1">
         <v>7412</v>
       </c>
@@ -7733,7 +7728,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="336" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:5">
       <c r="A336" s="1">
         <v>5036</v>
       </c>
@@ -7750,7 +7745,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="337" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:5">
       <c r="A337" s="1">
         <v>6678</v>
       </c>
@@ -7767,7 +7762,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="338" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:5">
       <c r="A338" s="1">
         <v>7464</v>
       </c>
@@ -7784,7 +7779,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="339" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:5">
       <c r="A339" s="1">
         <v>6020</v>
       </c>
@@ -7801,7 +7796,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="340" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:5">
       <c r="A340" s="1">
         <v>5761</v>
       </c>
@@ -7818,7 +7813,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="341" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:5">
       <c r="A341" s="1">
         <v>6549</v>
       </c>
@@ -7835,7 +7830,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="342" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:5">
       <c r="A342" s="1">
         <v>6593</v>
       </c>
@@ -7852,7 +7847,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="343" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:5">
       <c r="A343" s="1">
         <v>4349</v>
       </c>
@@ -7869,7 +7864,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="344" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:5">
       <c r="A344" s="1">
         <v>2528</v>
       </c>
@@ -7886,7 +7881,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="345" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:5">
       <c r="A345" s="1">
         <v>6170</v>
       </c>
@@ -7903,7 +7898,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="346" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:5">
       <c r="A346" s="1">
         <v>5674</v>
       </c>
@@ -7920,7 +7915,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="347" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:5">
       <c r="A347" s="1">
         <v>7146</v>
       </c>
@@ -7937,7 +7932,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="348" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:5">
       <c r="A348" s="1">
         <v>7528</v>
       </c>
@@ -7954,7 +7949,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="349" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:5">
       <c r="A349" s="1">
         <v>6640</v>
       </c>
@@ -7971,7 +7966,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="350" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:5">
       <c r="A350" s="1">
         <v>7127</v>
       </c>
@@ -7988,7 +7983,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="351" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:5">
       <c r="A351" s="1">
         <v>5998</v>
       </c>
@@ -8005,7 +8000,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="352" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:5">
       <c r="A352" s="1">
         <v>7341</v>
       </c>
@@ -8022,7 +8017,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="353" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:5">
       <c r="A353" s="1">
         <v>7409</v>
       </c>
@@ -8039,7 +8034,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="354" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:5">
       <c r="A354" s="1">
         <v>2857</v>
       </c>
@@ -8056,7 +8051,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="355" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:5">
       <c r="A355" s="1">
         <v>2529</v>
       </c>
@@ -8073,7 +8068,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="356" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:5">
       <c r="A356" s="1">
         <v>5685</v>
       </c>
@@ -8090,7 +8085,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="357" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:5">
       <c r="A357" s="1">
         <v>6629</v>
       </c>
@@ -8107,7 +8102,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="358" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:5">
       <c r="A358" s="1">
         <v>6015</v>
       </c>
@@ -8124,7 +8119,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="359" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:5">
       <c r="A359" s="1">
         <v>7318</v>
       </c>
@@ -8141,7 +8136,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="360" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:5">
       <c r="A360" s="1">
         <v>4686</v>
       </c>
@@ -8158,7 +8153,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="361" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:5">
       <c r="A361" s="1">
         <v>7203</v>
       </c>
@@ -8175,7 +8170,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="362" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:5">
       <c r="A362" s="1">
         <v>6898</v>
       </c>
@@ -8192,7 +8187,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="363" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:5">
       <c r="A363" s="1">
         <v>6677</v>
       </c>
@@ -8209,7 +8204,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="364" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:5">
       <c r="A364" s="1">
         <v>7036</v>
       </c>
@@ -8226,7 +8221,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="365" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:5">
       <c r="A365" s="1">
         <v>7060</v>
       </c>
@@ -8243,7 +8238,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="366" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:5">
       <c r="A366" s="1">
         <v>6827</v>
       </c>
@@ -8260,7 +8255,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="367" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:5">
       <c r="A367" s="1">
         <v>7198</v>
       </c>
@@ -8277,7 +8272,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="368" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:5">
       <c r="A368" s="1">
         <v>5507</v>
       </c>
@@ -8294,7 +8289,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="369" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:5">
       <c r="A369" s="1">
         <v>5319</v>
       </c>
@@ -8311,7 +8306,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="370" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:5">
       <c r="A370" s="1">
         <v>6994</v>
       </c>
@@ -8328,7 +8323,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="371" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:5">
       <c r="A371" s="1">
         <v>7550</v>
       </c>
@@ -8345,7 +8340,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="372" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:5">
       <c r="A372" s="1">
         <v>6618</v>
       </c>
@@ -8362,7 +8357,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="373" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:5">
       <c r="A373" s="1">
         <v>22</v>
       </c>
@@ -8379,7 +8374,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="374" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:5">
       <c r="A374" s="1">
         <v>6054</v>
       </c>
@@ -8396,7 +8391,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="375" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:5">
       <c r="A375" s="1">
         <v>6895</v>
       </c>
@@ -8413,7 +8408,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="376" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:5">
       <c r="A376" s="1">
         <v>1871</v>
       </c>
@@ -8430,7 +8425,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="377" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:5">
       <c r="A377" s="1">
         <v>6206</v>
       </c>
@@ -8447,7 +8442,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="378" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:5">
       <c r="A378" s="1">
         <v>7473</v>
       </c>
@@ -8464,7 +8459,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="379" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:5">
       <c r="A379" s="1">
         <v>7474</v>
       </c>
@@ -8481,7 +8476,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="380" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:5">
       <c r="A380" s="1">
         <v>6506</v>
       </c>
@@ -8498,7 +8493,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="381" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:5">
       <c r="A381" s="1">
         <v>4970</v>
       </c>
@@ -8515,7 +8510,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="382" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:5">
       <c r="A382" s="1">
         <v>5301</v>
       </c>
@@ -8532,7 +8527,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="383" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:5">
       <c r="A383" s="1">
         <v>4911</v>
       </c>
@@ -8549,7 +8544,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="384" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:5">
       <c r="A384" s="1">
         <v>333</v>
       </c>
@@ -8566,7 +8561,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="385" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:5">
       <c r="A385" s="1">
         <v>7322</v>
       </c>
@@ -8583,7 +8578,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="386" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:5">
       <c r="A386" s="1">
         <v>5453</v>
       </c>
@@ -8600,7 +8595,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="387" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:5">
       <c r="A387" s="1">
         <v>4199</v>
       </c>
@@ -8617,7 +8612,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="388" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:5">
       <c r="A388" s="1">
         <v>6252</v>
       </c>
@@ -8634,7 +8629,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="389" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:5">
       <c r="A389" s="1">
         <v>6207</v>
       </c>
@@ -8651,7 +8646,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="390" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:5">
       <c r="A390" s="1">
         <v>7536</v>
       </c>
@@ -8668,7 +8663,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="391" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:5">
       <c r="A391" s="1">
         <v>6271</v>
       </c>
@@ -8685,7 +8680,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="392" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:5">
       <c r="A392" s="1">
         <v>7535</v>
       </c>
@@ -8702,7 +8697,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="393" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:5">
       <c r="A393" s="1">
         <v>6005</v>
       </c>
@@ -8719,7 +8714,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="394" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:5">
       <c r="A394" s="1">
         <v>7208</v>
       </c>
@@ -8736,7 +8731,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="395" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:5">
       <c r="A395" s="1">
         <v>6024</v>
       </c>
@@ -8753,7 +8748,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="396" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:5">
       <c r="A396" s="1">
         <v>4947</v>
       </c>
@@ -8770,7 +8765,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="397" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:5">
       <c r="A397" s="1">
         <v>6241</v>
       </c>
@@ -8787,7 +8782,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="398" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:5">
       <c r="A398" s="1">
         <v>6903</v>
       </c>
@@ -8804,7 +8799,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="399" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:5">
       <c r="A399" s="1">
         <v>6917</v>
       </c>
@@ -8821,7 +8816,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="400" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:5">
       <c r="A400" s="1">
         <v>6503</v>
       </c>
@@ -8838,7 +8833,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="401" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:5">
       <c r="A401" s="1">
         <v>7248</v>
       </c>
@@ -8855,7 +8850,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="402" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:5">
       <c r="A402" s="1">
         <v>5457</v>
       </c>
@@ -8872,7 +8867,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="403" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:5">
       <c r="A403" s="1">
         <v>5295</v>
       </c>
@@ -8889,7 +8884,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="404" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:5">
       <c r="A404" s="1">
         <v>7477</v>
       </c>
@@ -8906,7 +8901,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="405" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:5">
       <c r="A405" s="1">
         <v>5131</v>
       </c>
@@ -8923,7 +8918,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="406" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:5">
       <c r="A406" s="1">
         <v>7138</v>
       </c>
@@ -8940,7 +8935,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="407" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:5">
       <c r="A407" s="1">
         <v>7209</v>
       </c>
@@ -8957,7 +8952,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="408" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:5">
       <c r="A408" s="1">
         <v>7183</v>
       </c>
@@ -8974,7 +8969,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="409" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:5">
       <c r="A409" s="1">
         <v>5872</v>
       </c>
@@ -8991,7 +8986,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="410" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:5">
       <c r="A410" s="1">
         <v>6225</v>
       </c>
@@ -9008,7 +9003,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="411" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:5">
       <c r="A411" s="1">
         <v>6815</v>
       </c>
@@ -9025,7 +9020,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="412" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:5">
       <c r="A412" s="1">
         <v>6980</v>
       </c>
@@ -9042,7 +9037,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="413" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:5">
       <c r="A413" s="1">
         <v>5880</v>
       </c>
@@ -9059,7 +9054,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="414" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:5">
       <c r="A414" s="1">
         <v>6219</v>
       </c>
@@ -9076,7 +9071,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="415" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:5">
       <c r="A415" s="1">
         <v>6246</v>
       </c>
@@ -9093,7 +9088,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="416" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:5">
       <c r="A416" s="1">
         <v>7418</v>
       </c>
@@ -9110,7 +9105,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="417" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:5">
       <c r="A417" s="1">
         <v>526</v>
       </c>
@@ -9127,7 +9122,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="418" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:5">
       <c r="A418" s="1">
         <v>6592</v>
       </c>
@@ -9144,7 +9139,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="419" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:5">
       <c r="A419" s="1">
         <v>7165</v>
       </c>
@@ -9161,7 +9156,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="420" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:5">
       <c r="A420" s="1">
         <v>7357</v>
       </c>
@@ -9178,7 +9173,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="421" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:5">
       <c r="A421" s="1">
         <v>7456</v>
       </c>
@@ -9195,7 +9190,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="422" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:5">
       <c r="A422" s="1">
         <v>5725</v>
       </c>
@@ -9212,7 +9207,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="423" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:5">
       <c r="A423" s="1">
         <v>6191</v>
       </c>
@@ -9229,7 +9224,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="424" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:5">
       <c r="A424" s="1">
         <v>7345</v>
       </c>
@@ -9246,7 +9241,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="425" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:5">
       <c r="A425" s="1">
         <v>6410</v>
       </c>
@@ -9263,7 +9258,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="426" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:5">
       <c r="A426" s="1">
         <v>7319</v>
       </c>
@@ -9280,7 +9275,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="427" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:5">
       <c r="A427" s="1">
         <v>7276</v>
       </c>
@@ -9297,7 +9292,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="428" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:5">
       <c r="A428" s="1">
         <v>7157</v>
       </c>
@@ -9314,7 +9309,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="429" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:5">
       <c r="A429" s="1">
         <v>5007</v>
       </c>
@@ -9331,7 +9326,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="430" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:5">
       <c r="A430" s="1">
         <v>6889</v>
       </c>
@@ -9348,7 +9343,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="431" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:5">
       <c r="A431" s="1">
         <v>6212</v>
       </c>
@@ -9365,7 +9360,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="432" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:5">
       <c r="A432" s="1">
         <v>7481</v>
       </c>
@@ -9382,7 +9377,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="433" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:5">
       <c r="A433" s="1">
         <v>7571</v>
       </c>
@@ -9399,7 +9394,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="434" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:5">
       <c r="A434" s="1">
         <v>7572</v>
       </c>
@@ -9416,7 +9411,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="435" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:5">
       <c r="A435" s="1">
         <v>7574</v>
       </c>
@@ -9433,7 +9428,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="436" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:5">
       <c r="A436" s="1">
         <v>7575</v>
       </c>
@@ -9450,7 +9445,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="437" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:5">
       <c r="A437" s="1">
         <v>5462</v>
       </c>
@@ -9467,7 +9462,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="438" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:5">
       <c r="A438" s="1">
         <v>5585</v>
       </c>
@@ -9484,7 +9479,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="439" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:5">
       <c r="A439" s="1">
         <v>2764</v>
       </c>
@@ -9501,7 +9496,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="440" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:5">
       <c r="A440" s="1">
         <v>4871</v>
       </c>
@@ -9518,7 +9513,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="441" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:5">
       <c r="A441" s="1">
         <v>6397</v>
       </c>
@@ -9535,7 +9530,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="442" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:5">
       <c r="A442" s="1">
         <v>6052</v>
       </c>
@@ -9552,7 +9547,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="443" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:5">
       <c r="A443" s="1">
         <v>2097</v>
       </c>
@@ -9569,7 +9564,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="444" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:5">
       <c r="A444" s="1">
         <v>5951</v>
       </c>
@@ -9586,7 +9581,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="445" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:5">
       <c r="A445" s="1">
         <v>6434</v>
       </c>
@@ -9603,7 +9598,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="446" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:5">
       <c r="A446" s="1">
         <v>7017</v>
       </c>
@@ -9620,7 +9615,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="447" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:5">
       <c r="A447" s="1">
         <v>6435</v>
       </c>
@@ -9637,7 +9632,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="448" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:5">
       <c r="A448" s="1">
         <v>2137</v>
       </c>
@@ -9654,7 +9649,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="449" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:5">
       <c r="A449" s="1">
         <v>5637</v>
       </c>
@@ -9671,7 +9666,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="450" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:5">
       <c r="A450" s="1">
         <v>531</v>
       </c>
@@ -9688,7 +9683,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="451" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:5">
       <c r="A451" s="1">
         <v>5995</v>
       </c>
@@ -9705,7 +9700,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="452" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:5">
       <c r="A452" s="1">
         <v>7071</v>
       </c>
@@ -9722,7 +9717,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="453" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:5">
       <c r="A453" s="1">
         <v>6675</v>
       </c>
@@ -9739,7 +9734,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="454" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:5">
       <c r="A454" s="1">
         <v>309</v>
       </c>
@@ -9756,7 +9751,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="455" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:5">
       <c r="A455" s="1">
         <v>6060</v>
       </c>
@@ -9773,7 +9768,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="456" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:5">
       <c r="A456" s="1">
         <v>2061</v>
       </c>
@@ -9790,7 +9785,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="457" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:5">
       <c r="A457" s="1">
         <v>4371</v>
       </c>
@@ -9807,7 +9802,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="458" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:5">
       <c r="A458" s="1">
         <v>7351</v>
       </c>
@@ -9824,7 +9819,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="459" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:5">
       <c r="A459" s="1">
         <v>7023</v>
       </c>
@@ -9841,7 +9836,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="460" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:5">
       <c r="A460" s="1">
         <v>6572</v>
       </c>
@@ -9858,7 +9853,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="461" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:5">
       <c r="A461" s="1">
         <v>4463</v>
       </c>
@@ -9875,7 +9870,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="462" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:5">
       <c r="A462" s="1">
         <v>2038</v>
       </c>
@@ -9892,7 +9887,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="463" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:5">
       <c r="A463" s="1">
         <v>7547</v>
       </c>
@@ -9909,7 +9904,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="464" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:5">
       <c r="A464" s="1">
         <v>5734</v>
       </c>
@@ -9926,7 +9921,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="465" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:5">
       <c r="A465" s="1">
         <v>7484</v>
       </c>
@@ -9943,7 +9938,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="466" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:5">
       <c r="A466" s="1">
         <v>6967</v>
       </c>
@@ -9960,7 +9955,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="467" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:5">
       <c r="A467" s="1">
         <v>4923</v>
       </c>
@@ -9977,7 +9972,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="468" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:5">
       <c r="A468" s="1">
         <v>6229</v>
       </c>
@@ -9994,7 +9989,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="469" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:5">
       <c r="A469" s="1">
         <v>5672</v>
       </c>
@@ -10011,7 +10006,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="470" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:5">
       <c r="A470" s="1">
         <v>7313</v>
       </c>
@@ -10028,7 +10023,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="471" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:5">
       <c r="A471" s="1">
         <v>7347</v>
       </c>
@@ -10045,7 +10040,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="472" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:5">
       <c r="A472" s="1">
         <v>6646</v>
       </c>
@@ -10062,7 +10057,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="473" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:5">
       <c r="A473" s="1">
         <v>7554</v>
       </c>
@@ -10079,7 +10074,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="474" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:5">
       <c r="A474" s="1">
         <v>6530</v>
       </c>
@@ -10096,7 +10091,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="475" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:5">
       <c r="A475" s="1">
         <v>5544</v>
       </c>
@@ -10113,7 +10108,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="476" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:5">
       <c r="A476" s="1">
         <v>5029</v>
       </c>
@@ -10130,7 +10125,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="477" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:5">
       <c r="A477" s="1">
         <v>2155</v>
       </c>
@@ -10147,7 +10142,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="478" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:5">
       <c r="A478" s="1">
         <v>7612</v>
       </c>
@@ -10164,7 +10159,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="479" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:5">
       <c r="A479" s="1">
         <v>4359</v>
       </c>
@@ -10181,7 +10176,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="480" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:5">
       <c r="A480" s="1">
         <v>6164</v>
       </c>
@@ -10198,7 +10193,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="481" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:5">
       <c r="A481" s="1">
         <v>6904</v>
       </c>
@@ -10215,7 +10210,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="482" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:5">
       <c r="A482" s="1">
         <v>7449</v>
       </c>
@@ -10232,7 +10227,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="483" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:5">
       <c r="A483" s="1">
         <v>7600</v>
       </c>
@@ -10249,7 +10244,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="484" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:5">
       <c r="A484" s="1">
         <v>5436</v>
       </c>
@@ -10266,7 +10261,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="485" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:5">
       <c r="A485" s="1">
         <v>6669</v>
       </c>
@@ -10283,7 +10278,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="486" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:5">
       <c r="A486" s="1">
         <v>7252</v>
       </c>
@@ -10300,7 +10295,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="487" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:5">
       <c r="A487" s="1">
         <v>608</v>
       </c>
@@ -10317,7 +10312,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="488" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:5">
       <c r="A488" s="1">
         <v>5918</v>
       </c>
@@ -10334,7 +10329,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="489" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:5">
       <c r="A489" s="1">
         <v>6598</v>
       </c>
@@ -10351,7 +10346,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="490" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:5">
       <c r="A490" s="1">
         <v>2832</v>
       </c>
@@ -10368,7 +10363,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="491" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:5">
       <c r="A491" s="1">
         <v>6556</v>
       </c>
@@ -10385,7 +10380,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="492" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:5">
       <c r="A492" s="1">
         <v>7008</v>
       </c>
@@ -10402,7 +10397,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="493" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:5">
       <c r="A493" s="1">
         <v>6831</v>
       </c>
@@ -10419,7 +10414,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="494" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:5">
       <c r="A494" s="1">
         <v>4896</v>
       </c>
@@ -10436,7 +10431,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="495" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:5">
       <c r="A495" s="1">
         <v>6519</v>
       </c>
@@ -10453,7 +10448,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="496" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:5">
       <c r="A496" s="1">
         <v>5882</v>
       </c>
@@ -10470,7 +10465,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="497" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:5">
       <c r="A497" s="1">
         <v>7523</v>
       </c>
@@ -10487,7 +10482,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="498" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:5">
       <c r="A498" s="1">
         <v>7213</v>
       </c>
@@ -10504,7 +10499,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="499" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:5">
       <c r="A499" s="1">
         <v>4387</v>
       </c>
@@ -10521,7 +10516,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="500" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:5">
       <c r="A500" s="1">
         <v>2012</v>
       </c>
@@ -10538,7 +10533,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="501" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:5">
       <c r="A501" s="1">
         <v>7610</v>
       </c>
@@ -10555,7 +10550,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="502" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:5">
       <c r="A502" s="1">
         <v>6145</v>
       </c>
@@ -10572,7 +10567,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="503" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:5">
       <c r="A503" s="1">
         <v>6243</v>
       </c>
@@ -10589,7 +10584,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="504" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:5">
       <c r="A504" s="1">
         <v>7374</v>
       </c>
@@ -10606,7 +10601,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="505" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:5">
       <c r="A505" s="1">
         <v>6204</v>
       </c>
@@ -10623,7 +10618,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="506" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:5">
       <c r="A506" s="1">
         <v>7453</v>
       </c>
@@ -10640,7 +10635,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="507" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:5">
       <c r="A507" s="1">
         <v>7162</v>
       </c>
@@ -10657,7 +10652,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="508" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:5">
       <c r="A508" s="1">
         <v>7120</v>
       </c>
@@ -10674,7 +10669,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="509" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:5">
       <c r="A509" s="1">
         <v>6215</v>
       </c>
@@ -10691,7 +10686,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="510" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:5">
       <c r="A510" s="1">
         <v>7349</v>
       </c>
@@ -10708,7 +10703,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="511" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:5">
       <c r="A511" s="1">
         <v>7272</v>
       </c>
@@ -10725,7 +10720,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="512" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:5">
       <c r="A512" s="1">
         <v>7546</v>
       </c>
@@ -10742,7 +10737,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="513" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:5">
       <c r="A513" s="1">
         <v>7602</v>
       </c>
@@ -10759,7 +10754,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="514" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:5">
       <c r="A514" s="1">
         <v>7128</v>
       </c>
@@ -10776,7 +10771,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="515" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:5">
       <c r="A515" s="1">
         <v>6822</v>
       </c>
@@ -10793,7 +10788,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="516" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:5">
       <c r="A516" s="1">
         <v>7001</v>
       </c>
@@ -10810,7 +10805,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="517" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:5">
       <c r="A517" s="1">
         <v>7342</v>
       </c>
@@ -10827,7 +10822,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="518" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:5">
       <c r="A518" s="1">
         <v>7561</v>
       </c>
@@ -10844,7 +10839,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="519" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:5">
       <c r="A519" s="1">
         <v>7317</v>
       </c>
@@ -10861,7 +10856,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="520" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:5">
       <c r="A520" s="1">
         <v>7027</v>
       </c>
@@ -10878,7 +10873,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="521" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:5">
       <c r="A521" s="1">
         <v>6981</v>
       </c>
@@ -10895,7 +10890,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="522" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:5">
       <c r="A522" s="1">
         <v>7161</v>
       </c>
@@ -10912,7 +10907,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="523" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:5">
       <c r="A523" s="1">
         <v>7408</v>
       </c>
@@ -10929,7 +10924,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="524" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:5">
       <c r="A524" s="1">
         <v>7482</v>
       </c>
@@ -10946,7 +10941,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="525" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:5">
       <c r="A525" s="1">
         <v>7568</v>
       </c>
